--- a/Project_ETF/ETF_Investment_Portfolio/009805/ETF_Investment_Portfolio_20260617.xlsx
+++ b/Project_ETF/ETF_Investment_Portfolio/009805/ETF_Investment_Portfolio_20260617.xlsx
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D71"/>
+  <dimension ref="A1:D72"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24.75" customWidth="1" min="1" max="1"/>
@@ -601,44 +601,44 @@
     <row r="21">
       <c r="A21" s="3" t="inlineStr">
         <is>
-          <t>ETN US</t>
+          <t>GEV US</t>
         </is>
       </c>
       <c r="B21" s="3" t="inlineStr">
         <is>
-          <t>伊頓公開有限公司</t>
+          <t>奇異維諾瓦公司</t>
         </is>
       </c>
       <c r="C21" s="4" t="inlineStr">
         <is>
-          <t>87,630</t>
+          <t>36,253</t>
         </is>
       </c>
       <c r="D21" s="4" t="inlineStr">
         <is>
-          <t>10.02%</t>
+          <t>10.60%</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="3" t="inlineStr">
         <is>
-          <t>GEV US</t>
+          <t>ETN US</t>
         </is>
       </c>
       <c r="B22" s="3" t="inlineStr">
         <is>
-          <t>奇異維諾瓦公司</t>
+          <t>伊頓公開有限公司</t>
         </is>
       </c>
       <c r="C22" s="4" t="inlineStr">
         <is>
-          <t>36,253</t>
+          <t>87,630</t>
         </is>
       </c>
       <c r="D22" s="4" t="inlineStr">
         <is>
-          <t>9.99%</t>
+          <t>10.00%</t>
         </is>
       </c>
     </row>
@@ -660,7 +660,7 @@
       </c>
       <c r="D23" s="4" t="inlineStr">
         <is>
-          <t>8.49%</t>
+          <t>8.95%</t>
         </is>
       </c>
     </row>
@@ -682,7 +682,7 @@
       </c>
       <c r="D24" s="4" t="inlineStr">
         <is>
-          <t>8.03%</t>
+          <t>7.93%</t>
         </is>
       </c>
     </row>
@@ -704,7 +704,7 @@
       </c>
       <c r="D25" s="4" t="inlineStr">
         <is>
-          <t>5.28%</t>
+          <t>5.22%</t>
         </is>
       </c>
     </row>
@@ -726,7 +726,7 @@
       </c>
       <c r="D26" s="4" t="inlineStr">
         <is>
-          <t>4.32%</t>
+          <t>4.35%</t>
         </is>
       </c>
     </row>
@@ -748,7 +748,7 @@
       </c>
       <c r="D27" s="4" t="inlineStr">
         <is>
-          <t>4.11%</t>
+          <t>4.00%</t>
         </is>
       </c>
     </row>
@@ -770,7 +770,7 @@
       </c>
       <c r="D28" s="4" t="inlineStr">
         <is>
-          <t>3.33%</t>
+          <t>3.25%</t>
         </is>
       </c>
     </row>
@@ -792,7 +792,7 @@
       </c>
       <c r="D29" s="4" t="inlineStr">
         <is>
-          <t>3.10%</t>
+          <t>3.14%</t>
         </is>
       </c>
     </row>
@@ -814,7 +814,7 @@
       </c>
       <c r="D30" s="4" t="inlineStr">
         <is>
-          <t>3.06%</t>
+          <t>3.08%</t>
         </is>
       </c>
     </row>
@@ -836,7 +836,7 @@
       </c>
       <c r="D31" s="4" t="inlineStr">
         <is>
-          <t>2.52%</t>
+          <t>2.48%</t>
         </is>
       </c>
     </row>
@@ -858,51 +858,51 @@
       </c>
       <c r="D32" s="4" t="inlineStr">
         <is>
-          <t>2.21%</t>
+          <t>2.17%</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="3" t="inlineStr">
         <is>
-          <t>FSLR US</t>
+          <t>EXC US</t>
         </is>
       </c>
       <c r="B33" s="3" t="inlineStr">
         <is>
-          <t>第一太陽能</t>
+          <t>Exelon Corp</t>
         </is>
       </c>
       <c r="C33" s="4" t="inlineStr">
         <is>
-          <t>27,197</t>
+          <t>152,528</t>
         </is>
       </c>
       <c r="D33" s="4" t="inlineStr">
         <is>
-          <t>2.02%</t>
+          <t>1.94%</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="3" t="inlineStr">
         <is>
-          <t>EXC US</t>
+          <t>FSLR US</t>
         </is>
       </c>
       <c r="B34" s="3" t="inlineStr">
         <is>
-          <t>Exelon Corp</t>
+          <t>第一太陽能</t>
         </is>
       </c>
       <c r="C34" s="4" t="inlineStr">
         <is>
-          <t>152,528</t>
+          <t>27,197</t>
         </is>
       </c>
       <c r="D34" s="4" t="inlineStr">
         <is>
-          <t>1.99%</t>
+          <t>1.93%</t>
         </is>
       </c>
     </row>
@@ -924,7 +924,7 @@
       </c>
       <c r="D35" s="4" t="inlineStr">
         <is>
-          <t>1.89%</t>
+          <t>1.88%</t>
         </is>
       </c>
     </row>
@@ -946,7 +946,7 @@
       </c>
       <c r="D36" s="4" t="inlineStr">
         <is>
-          <t>1.54%</t>
+          <t>1.51%</t>
         </is>
       </c>
     </row>
@@ -968,7 +968,7 @@
       </c>
       <c r="D37" s="4" t="inlineStr">
         <is>
-          <t>1.31%</t>
+          <t>1.33%</t>
         </is>
       </c>
     </row>
@@ -990,7 +990,7 @@
       </c>
       <c r="D38" s="4" t="inlineStr">
         <is>
-          <t>1.26%</t>
+          <t>1.23%</t>
         </is>
       </c>
     </row>
@@ -1012,7 +1012,7 @@
       </c>
       <c r="D39" s="4" t="inlineStr">
         <is>
-          <t>1.25%</t>
+          <t>1.23%</t>
         </is>
       </c>
     </row>
@@ -1034,7 +1034,7 @@
       </c>
       <c r="D40" s="4" t="inlineStr">
         <is>
-          <t>1.17%</t>
+          <t>1.14%</t>
         </is>
       </c>
     </row>
@@ -1056,7 +1056,7 @@
       </c>
       <c r="D41" s="4" t="inlineStr">
         <is>
-          <t>1.16%</t>
+          <t>1.13%</t>
         </is>
       </c>
     </row>
@@ -1078,46 +1078,46 @@
       </c>
       <c r="D42" s="4" t="inlineStr">
         <is>
-          <t>1.15%</t>
+          <t>1.11%</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="3" t="inlineStr">
         <is>
-          <t>VST US</t>
+          <t>AGX US</t>
         </is>
       </c>
       <c r="B43" s="3" t="inlineStr">
         <is>
-          <t>維斯達能源公司</t>
+          <t>阿根公司</t>
         </is>
       </c>
       <c r="C43" s="4" t="inlineStr">
         <is>
-          <t>24,908</t>
+          <t>5,507</t>
         </is>
       </c>
       <c r="D43" s="4" t="inlineStr">
         <is>
-          <t>1.11%</t>
+          <t>1.10%</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="3" t="inlineStr">
         <is>
-          <t>ES US</t>
+          <t>VST US</t>
         </is>
       </c>
       <c r="B44" s="3" t="inlineStr">
         <is>
-          <t>Eversource能源</t>
+          <t>維斯達能源公司</t>
         </is>
       </c>
       <c r="C44" s="4" t="inlineStr">
         <is>
-          <t>56,020</t>
+          <t>24,908</t>
         </is>
       </c>
       <c r="D44" s="4" t="inlineStr">
@@ -1129,44 +1129,44 @@
     <row r="45">
       <c r="A45" s="3" t="inlineStr">
         <is>
-          <t>ETR US</t>
+          <t>ES US</t>
         </is>
       </c>
       <c r="B45" s="3" t="inlineStr">
         <is>
-          <t>安特吉公司</t>
+          <t>Eversource能源</t>
         </is>
       </c>
       <c r="C45" s="4" t="inlineStr">
         <is>
-          <t>34,069</t>
+          <t>56,020</t>
         </is>
       </c>
       <c r="D45" s="4" t="inlineStr">
         <is>
-          <t>1.07%</t>
+          <t>1.08%</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="3" t="inlineStr">
         <is>
-          <t>AGX US</t>
+          <t>ETR US</t>
         </is>
       </c>
       <c r="B46" s="3" t="inlineStr">
         <is>
-          <t>阿根公司</t>
+          <t>安特吉公司</t>
         </is>
       </c>
       <c r="C46" s="4" t="inlineStr">
         <is>
-          <t>5,507</t>
+          <t>34,069</t>
         </is>
       </c>
       <c r="D46" s="4" t="inlineStr">
         <is>
-          <t>1.07%</t>
+          <t>1.05%</t>
         </is>
       </c>
     </row>
@@ -1188,7 +1188,7 @@
       </c>
       <c r="D47" s="4" t="inlineStr">
         <is>
-          <t>1.05%</t>
+          <t>1.02%</t>
         </is>
       </c>
     </row>
@@ -1232,46 +1232,46 @@
       </c>
       <c r="D49" s="4" t="inlineStr">
         <is>
-          <t>0.97%</t>
+          <t>0.95%</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="3" t="inlineStr">
         <is>
-          <t>AEE US</t>
+          <t>ENS US</t>
         </is>
       </c>
       <c r="B50" s="3" t="inlineStr">
         <is>
-          <t>阿莫林公司</t>
+          <t>EnerSys</t>
         </is>
       </c>
       <c r="C50" s="4" t="inlineStr">
         <is>
-          <t>30,851</t>
+          <t>14,830</t>
         </is>
       </c>
       <c r="D50" s="4" t="inlineStr">
         <is>
-          <t>0.96%</t>
+          <t>0.94%</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="3" t="inlineStr">
         <is>
-          <t>ENS US</t>
+          <t>AEE US</t>
         </is>
       </c>
       <c r="B51" s="3" t="inlineStr">
         <is>
-          <t>EnerSys</t>
+          <t>阿莫林公司</t>
         </is>
       </c>
       <c r="C51" s="4" t="inlineStr">
         <is>
-          <t>14,830</t>
+          <t>30,851</t>
         </is>
       </c>
       <c r="D51" s="4" t="inlineStr">
@@ -1320,7 +1320,7 @@
       </c>
       <c r="D53" s="4" t="inlineStr">
         <is>
-          <t>0.86%</t>
+          <t>0.83%</t>
         </is>
       </c>
     </row>
@@ -1342,7 +1342,7 @@
       </c>
       <c r="D54" s="4" t="inlineStr">
         <is>
-          <t>0.85%</t>
+          <t>0.83%</t>
         </is>
       </c>
     </row>
@@ -1364,7 +1364,7 @@
       </c>
       <c r="D55" s="4" t="inlineStr">
         <is>
-          <t>0.80%</t>
+          <t>0.78%</t>
         </is>
       </c>
     </row>
@@ -1386,7 +1386,7 @@
       </c>
       <c r="D56" s="4" t="inlineStr">
         <is>
-          <t>0.77%</t>
+          <t>0.75%</t>
         </is>
       </c>
     </row>
@@ -1408,7 +1408,7 @@
       </c>
       <c r="D57" s="4" t="inlineStr">
         <is>
-          <t>0.71%</t>
+          <t>0.70%</t>
         </is>
       </c>
     </row>
@@ -1430,7 +1430,7 @@
       </c>
       <c r="D58" s="4" t="inlineStr">
         <is>
-          <t>0.64%</t>
+          <t>0.63%</t>
         </is>
       </c>
     </row>
@@ -1459,17 +1459,17 @@
     <row r="60">
       <c r="A60" s="3" t="inlineStr">
         <is>
-          <t>LNT US</t>
+          <t>VICR US</t>
         </is>
       </c>
       <c r="B60" s="3" t="inlineStr">
         <is>
-          <t>聯合能源公司</t>
+          <t>懷克爾公司</t>
         </is>
       </c>
       <c r="C60" s="4" t="inlineStr">
         <is>
-          <t>28,850</t>
+          <t>6,577</t>
         </is>
       </c>
       <c r="D60" s="4" t="inlineStr">
@@ -1481,17 +1481,17 @@
     <row r="61">
       <c r="A61" s="3" t="inlineStr">
         <is>
-          <t>CNP US</t>
+          <t>LNT US</t>
         </is>
       </c>
       <c r="B61" s="3" t="inlineStr">
         <is>
-          <t>Centerpoint能源</t>
+          <t>聯合能源公司</t>
         </is>
       </c>
       <c r="C61" s="4" t="inlineStr">
         <is>
-          <t>48,660</t>
+          <t>28,850</t>
         </is>
       </c>
       <c r="D61" s="4" t="inlineStr">
@@ -1503,22 +1503,22 @@
     <row r="62">
       <c r="A62" s="3" t="inlineStr">
         <is>
-          <t>VICR US</t>
+          <t>CNP US</t>
         </is>
       </c>
       <c r="B62" s="3" t="inlineStr">
         <is>
-          <t>懷克爾公司</t>
+          <t>Centerpoint能源</t>
         </is>
       </c>
       <c r="C62" s="4" t="inlineStr">
         <is>
-          <t>6,577</t>
+          <t>48,660</t>
         </is>
       </c>
       <c r="D62" s="4" t="inlineStr">
         <is>
-          <t>0.59%</t>
+          <t>0.58%</t>
         </is>
       </c>
     </row>
@@ -1540,46 +1540,46 @@
       </c>
       <c r="D63" s="4" t="inlineStr">
         <is>
-          <t>0.56%</t>
+          <t>0.55%</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="3" t="inlineStr">
         <is>
-          <t>PNW US</t>
+          <t>MYRG US</t>
         </is>
       </c>
       <c r="B64" s="3" t="inlineStr">
         <is>
-          <t>皮那可資本公司</t>
+          <t>MYR集團公司</t>
         </is>
       </c>
       <c r="C64" s="4" t="inlineStr">
         <is>
-          <t>18,047</t>
+          <t>4,086</t>
         </is>
       </c>
       <c r="D64" s="4" t="inlineStr">
         <is>
-          <t>0.53%</t>
+          <t>0.51%</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="3" t="inlineStr">
         <is>
-          <t>MYRG US</t>
+          <t>PNW US</t>
         </is>
       </c>
       <c r="B65" s="3" t="inlineStr">
         <is>
-          <t>MYR集團公司</t>
+          <t>皮那可資本公司</t>
         </is>
       </c>
       <c r="C65" s="4" t="inlineStr">
         <is>
-          <t>4,086</t>
+          <t>18,047</t>
         </is>
       </c>
       <c r="D65" s="4" t="inlineStr">
@@ -1628,7 +1628,7 @@
       </c>
       <c r="D67" s="4" t="inlineStr">
         <is>
-          <t>0.37%</t>
+          <t>0.35%</t>
         </is>
       </c>
     </row>
@@ -1650,7 +1650,7 @@
       </c>
       <c r="D68" s="4" t="inlineStr">
         <is>
-          <t>0.26%</t>
+          <t>0.27%</t>
         </is>
       </c>
     </row>
@@ -1694,7 +1694,7 @@
       </c>
       <c r="D70" s="4" t="inlineStr">
         <is>
-          <t>0.14%</t>
+          <t>0.13%</t>
         </is>
       </c>
     </row>
@@ -1719,6 +1719,20 @@
           <t>0.02%</t>
         </is>
       </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="3" t="inlineStr">
+        <is>
+          <t>C_NTD</t>
+        </is>
+      </c>
+      <c r="B72" s="3" t="inlineStr"/>
+      <c r="C72" s="4" t="inlineStr">
+        <is>
+          <t>124,882,004</t>
+        </is>
+      </c>
+      <c r="D72" s="4" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="5">
